--- a/Assets/Resources/Configs/Excel/MonsterConfig.xlsx
+++ b/Assets/Resources/Configs/Excel/MonsterConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28700" windowHeight="13040"/>
+    <workbookView windowWidth="28680" windowHeight="12620"/>
   </bookViews>
   <sheets>
     <sheet name="Monster" sheetId="1" r:id="rId1"/>
@@ -692,7 +692,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="N4">
         <v>1</v>
